--- a/data/processed/inventory_ageing_AA_Tonor.xlsx
+++ b/data/processed/inventory_ageing_AA_Tonor.xlsx
@@ -776,23 +776,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79903</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0FR5DLXH9</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -804,10 +804,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>87.28</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -816,30 +816,30 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AA-25M</t>
+          <t>AM-C50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79903</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0FR5DLXH9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -851,10 +851,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>87.28</v>
+        <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AA-25M</t>
         </is>
       </c>
     </row>
@@ -1199,23 +1199,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1227,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>31.32</v>
+        <v>1195.88</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1239,30 +1239,30 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1195.88</v>
+        <v>31.32</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>AM-C43</t>
         </is>
       </c>
     </row>
@@ -3455,23 +3455,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3483,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3495,30 +3495,30 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AA-20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3530,10 +3530,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AM-W33</t>
         </is>
       </c>
     </row>
